--- a/data/trans_orig/Q4502_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q4502_R-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron camiseta para protegerse del sol el pasado verano al aire libre en 2007</t>
+          <t>Población según la frecuencia con la que utilizaron camiseta para protegerse del sol el pasado verano al aire libre en 2007 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>305718</t>
+          <t>303463</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>362370</t>
+          <t>362754</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>331467</t>
+          <t>327643</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>395727</t>
+          <t>393343</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>654751</t>
+          <t>650658</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>740680</t>
+          <t>738820</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,52%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>171202</t>
+          <t>168754</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>219129</t>
+          <t>220268</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>210130</t>
+          <t>211077</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>267448</t>
+          <t>265752</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>394650</t>
+          <t>393808</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>468425</t>
+          <t>468536</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>204557</t>
+          <t>205596</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>256876</t>
+          <t>259648</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>273516</t>
+          <t>271464</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>333584</t>
+          <t>331599</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>491581</t>
+          <t>494430</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>573253</t>
+          <t>573455</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38835</t>
+          <t>38844</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66908</t>
+          <t>65810</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56945</t>
+          <t>57949</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>88173</t>
+          <t>90971</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>103798</t>
+          <t>103149</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>147129</t>
+          <t>146542</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>195905</t>
+          <t>194020</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>246827</t>
+          <t>247434</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>309892</t>
+          <t>309428</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370255</t>
+          <t>372022</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>521241</t>
+          <t>524362</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>605715</t>
+          <t>604739</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>252452</t>
+          <t>250810</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>311600</t>
+          <t>315162</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>205482</t>
+          <t>205489</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>261167</t>
+          <t>260817</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>473427</t>
+          <t>474589</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>558399</t>
+          <t>554602</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,93%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>395218</t>
+          <t>396977</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>464468</t>
+          <t>466690</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>247509</t>
+          <t>249494</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>307747</t>
+          <t>310057</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>660044</t>
+          <t>660587</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>754381</t>
+          <t>758826</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>517530</t>
+          <t>512957</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>596253</t>
+          <t>592531</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>494626</t>
+          <t>496734</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>569801</t>
+          <t>568935</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1038283</t>
+          <t>1038788</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1141494</t>
+          <t>1138804</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,77%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82011</t>
+          <t>81235</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119627</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>118523</t>
+          <t>118277</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>162513</t>
+          <t>161162</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>211144</t>
+          <t>211308</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>270920</t>
+          <t>268159</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>292528</t>
+          <t>290905</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>356411</t>
+          <t>362359</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>368033</t>
+          <t>368044</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>435291</t>
+          <t>435249</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>682041</t>
+          <t>682209</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>778280</t>
+          <t>774765</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85903</t>
+          <t>85755</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>124046</t>
+          <t>124968</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67450</t>
+          <t>67461</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>101724</t>
+          <t>103134</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>164225</t>
+          <t>162915</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>214998</t>
+          <t>214959</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,91%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>109246</t>
+          <t>108615</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>149963</t>
+          <t>149253</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79439</t>
+          <t>79789</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>113666</t>
+          <t>115197</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>197398</t>
+          <t>197890</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>250050</t>
+          <t>251144</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>160489</t>
+          <t>158345</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>201367</t>
+          <t>206022</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>139393</t>
+          <t>138001</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>181018</t>
+          <t>180897</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>309305</t>
+          <t>310239</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>372107</t>
+          <t>370423</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,04%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33721</t>
+          <t>33375</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61279</t>
+          <t>58781</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33604</t>
+          <t>35322</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60813</t>
+          <t>63193</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>73784</t>
+          <t>74146</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>113530</t>
+          <t>109743</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>76332</t>
+          <t>76986</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>110912</t>
+          <t>113563</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>74859</t>
+          <t>72572</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>108672</t>
+          <t>108091</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>159308</t>
+          <t>161187</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>208275</t>
+          <t>209284</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>668751</t>
+          <t>671434</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>769891</t>
+          <t>767657</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>632389</t>
+          <t>634255</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>725137</t>
+          <t>731378</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1336445</t>
+          <t>1330014</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1466128</t>
+          <t>1460295</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>700889</t>
+          <t>702665</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>797745</t>
+          <t>803949</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>570474</t>
+          <t>575402</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>656808</t>
+          <t>666360</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1297411</t>
+          <t>1300068</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1430888</t>
+          <t>1431197</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>913899</t>
+          <t>913761</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1022106</t>
+          <t>1020629</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>939944</t>
+          <t>929846</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1048297</t>
+          <t>1043322</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1882771</t>
+          <t>1888742</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2037094</t>
+          <t>2037541</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>168499</t>
+          <t>168536</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>224723</t>
+          <t>222029</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>227976</t>
+          <t>229760</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>292760</t>
+          <t>288571</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>414695</t>
+          <t>411947</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>495749</t>
+          <t>493046</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>594178</t>
+          <t>592539</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>686520</t>
+          <t>683628</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>780637</t>
+          <t>775347</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>879963</t>
+          <t>876210</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,47 +3280,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
+          <t>22,98%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>25,97%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1471670</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>1402924</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>1538111</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>22,14%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>21,11%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>23,14%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>26,08%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1449</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1471670</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1406372</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1535282</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>22,14%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>21,16%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>23,1%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron camiseta para protegerse del sol el pasado verano al aire libre en 2012</t>
+          <t>Población según la frecuencia con la que utilizaron camiseta para protegerse del sol el pasado verano al aire libre en 2012 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>459563</t>
+          <t>457962</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>523782</t>
+          <t>522985</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>640895</t>
+          <t>639983</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>712584</t>
+          <t>717841</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1120660</t>
+          <t>1118812</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1219177</t>
+          <t>1211418</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,44%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>138334</t>
+          <t>136465</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>184808</t>
+          <t>185651</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>162089</t>
+          <t>159602</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>214800</t>
+          <t>212753</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>312115</t>
+          <t>316027</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>384004</t>
+          <t>382618</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>78934</t>
+          <t>79051</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>117335</t>
+          <t>116496</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>108769</t>
+          <t>109272</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>156307</t>
+          <t>155120</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>199585</t>
+          <t>201929</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>259859</t>
+          <t>261436</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24831</t>
+          <t>25140</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50562</t>
+          <t>50791</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32705</t>
+          <t>32823</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60761</t>
+          <t>60238</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63828</t>
+          <t>65303</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101634</t>
+          <t>99999</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>166967</t>
+          <t>165107</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>216936</t>
+          <t>216286</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>267610</t>
+          <t>268221</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>329112</t>
+          <t>333457</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>451820</t>
+          <t>450158</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>531553</t>
+          <t>532645</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>655114</t>
+          <t>656943</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>744078</t>
+          <t>745661</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>501618</t>
+          <t>505008</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>581951</t>
+          <t>580166</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1186933</t>
+          <t>1184937</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1299379</t>
+          <t>1308245</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,23%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>421674</t>
+          <t>420222</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>497366</t>
+          <t>498892</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>327238</t>
+          <t>328389</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>397856</t>
+          <t>397253</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>768096</t>
+          <t>766328</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>872508</t>
+          <t>870329</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>344479</t>
+          <t>341549</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>415266</t>
+          <t>417018</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>311534</t>
+          <t>309041</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>379334</t>
+          <t>376669</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>673136</t>
+          <t>675191</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>774327</t>
+          <t>776406</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,91%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74690</t>
+          <t>72325</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112019</t>
+          <t>112711</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>122783</t>
+          <t>122920</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>171723</t>
+          <t>170953</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>209471</t>
+          <t>209766</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>272017</t>
+          <t>269211</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>296301</t>
+          <t>292739</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365068</t>
+          <t>362962</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>326032</t>
+          <t>323920</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>395195</t>
+          <t>394272</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>639238</t>
+          <t>645218</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>738943</t>
+          <t>743521</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>140157</t>
+          <t>137912</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>183384</t>
+          <t>181586</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>139169</t>
+          <t>137672</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>182305</t>
+          <t>181130</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>291066</t>
+          <t>288145</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>349982</t>
+          <t>348329</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,21%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>98704</t>
+          <t>100099</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>140136</t>
+          <t>142765</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73759</t>
+          <t>75273</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>111134</t>
+          <t>112325</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>183806</t>
+          <t>186213</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>240530</t>
+          <t>240631</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,71%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>92754</t>
+          <t>92839</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>131376</t>
+          <t>133395</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>83169</t>
+          <t>84595</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>122850</t>
+          <t>121873</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>190495</t>
+          <t>186671</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>241782</t>
+          <t>239624</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17413</t>
+          <t>17064</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39006</t>
+          <t>37760</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26338</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49507</t>
+          <t>50967</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50443</t>
+          <t>49653</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81553</t>
+          <t>81243</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50494</t>
+          <t>50091</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>81839</t>
+          <t>83174</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51409</t>
+          <t>50545</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>83620</t>
+          <t>83061</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>106366</t>
+          <t>109184</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>152672</t>
+          <t>154233</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1290303</t>
+          <t>1293263</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1415692</t>
+          <t>1407439</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1315273</t>
+          <t>1316598</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1438714</t>
+          <t>1439388</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2632968</t>
+          <t>2634298</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2811536</t>
+          <t>2807824</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,34%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>692808</t>
+          <t>691012</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>794482</t>
+          <t>789748</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>593897</t>
+          <t>594408</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>688580</t>
+          <t>685999</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1315902</t>
+          <t>1309119</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1444085</t>
+          <t>1447021</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,79%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>543309</t>
+          <t>542828</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>635270</t>
+          <t>634222</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>532304</t>
+          <t>533374</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>621138</t>
+          <t>618643</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1098912</t>
+          <t>1098594</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1226197</t>
+          <t>1229560</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>132024</t>
+          <t>133417</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>180605</t>
+          <t>181315</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>202080</t>
+          <t>201355</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>262465</t>
+          <t>260062</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>346326</t>
+          <t>338753</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>424328</t>
+          <t>421555</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>541268</t>
+          <t>537435</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>635108</t>
+          <t>630697</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>674946</t>
+          <t>673846</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>773641</t>
+          <t>773473</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1240745</t>
+          <t>1243496</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1371457</t>
+          <t>1379705</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron camiseta para protegerse del sol el pasado verano al aire libre en 2016</t>
+          <t>Población según la frecuencia con la que utilizaron camiseta para protegerse del sol el pasado verano al aire libre en 2016 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>194263</t>
+          <t>193033</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>241525</t>
+          <t>242934</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>263967</t>
+          <t>264031</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>326180</t>
+          <t>326261</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>469291</t>
+          <t>472813</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>551021</t>
+          <t>551385</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,61%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>224019</t>
+          <t>224525</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>274810</t>
+          <t>276682</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>253243</t>
+          <t>257224</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>314391</t>
+          <t>317180</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>494199</t>
+          <t>497219</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>572061</t>
+          <t>577898</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>101228</t>
+          <t>101272</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>140812</t>
+          <t>141756</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>116353</t>
+          <t>114315</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>158266</t>
+          <t>159324</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>232557</t>
+          <t>230022</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>293526</t>
+          <t>291906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17640</t>
+          <t>16964</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39191</t>
+          <t>37089</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28068</t>
+          <t>28817</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54684</t>
+          <t>54831</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49961</t>
+          <t>49916</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83184</t>
+          <t>82703</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>116629</t>
+          <t>119654</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>157940</t>
+          <t>160163</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>210842</t>
+          <t>213539</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>268971</t>
+          <t>269800</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>343037</t>
+          <t>343105</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>415428</t>
+          <t>413924</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>437396</t>
+          <t>437353</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>517167</t>
+          <t>522459</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>382006</t>
+          <t>385074</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>456253</t>
+          <t>456778</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>842967</t>
+          <t>841581</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>952733</t>
+          <t>953280</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,56%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>597414</t>
+          <t>596840</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>682481</t>
+          <t>685562</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>584235</t>
+          <t>585728</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>667280</t>
+          <t>671218</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1210430</t>
+          <t>1207211</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1327122</t>
+          <t>1329170</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,85%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>493066</t>
+          <t>492721</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>573851</t>
+          <t>567957</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>401836</t>
+          <t>401148</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>477695</t>
+          <t>477823</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>909031</t>
+          <t>913679</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1023805</t>
+          <t>1021798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>109981</t>
+          <t>110085</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>155508</t>
+          <t>155265</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>122957</t>
+          <t>123563</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>170766</t>
+          <t>170677</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>244160</t>
+          <t>241267</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>307793</t>
+          <t>308404</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>257175</t>
+          <t>256758</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>319955</t>
+          <t>321749</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>318676</t>
+          <t>320077</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>388102</t>
+          <t>387613</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>597987</t>
+          <t>594547</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>693642</t>
+          <t>686481</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>109300</t>
+          <t>108494</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>149965</t>
+          <t>148228</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>104765</t>
+          <t>103486</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>144470</t>
+          <t>144468</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>222131</t>
+          <t>223868</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>279682</t>
+          <t>281679</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,79%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>181293</t>
+          <t>178846</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>227038</t>
+          <t>226033</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>127782</t>
+          <t>123388</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>171087</t>
+          <t>169470</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>318794</t>
+          <t>317724</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>381682</t>
+          <t>379958</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96423</t>
+          <t>98619</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>136823</t>
+          <t>137703</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>107902</t>
+          <t>108595</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>148480</t>
+          <t>148452</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>218247</t>
+          <t>219284</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274560</t>
+          <t>274348</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,12%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21877</t>
+          <t>21863</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45458</t>
+          <t>44248</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29209</t>
+          <t>30357</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56673</t>
+          <t>56011</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58237</t>
+          <t>56465</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>92675</t>
+          <t>91830</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>47645</t>
+          <t>47285</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>77863</t>
+          <t>79591</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>92466</t>
+          <t>92045</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>132623</t>
+          <t>131703</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>147226</t>
+          <t>148649</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>197044</t>
+          <t>199686</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>767895</t>
+          <t>773716</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>871431</t>
+          <t>872934</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>776880</t>
+          <t>783132</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>889546</t>
+          <t>881751</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1587848</t>
+          <t>1586580</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1732276</t>
+          <t>1736116</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1037049</t>
+          <t>1035492</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1151053</t>
+          <t>1147853</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>998773</t>
+          <t>1003908</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1111790</t>
+          <t>1115380</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2069236</t>
+          <t>2072351</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2225747</t>
+          <t>2227707</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,37%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>720650</t>
+          <t>722357</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>821769</t>
+          <t>820400</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>651077</t>
+          <t>653981</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>748479</t>
+          <t>746642</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1403842</t>
+          <t>1408513</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1541733</t>
+          <t>1543978</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,43%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>162589</t>
+          <t>163177</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>220663</t>
+          <t>217221</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>199463</t>
+          <t>198582</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>254526</t>
+          <t>256435</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>370454</t>
+          <t>375185</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>454706</t>
+          <t>459141</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>448249</t>
+          <t>450306</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>532312</t>
+          <t>533695</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>656013</t>
+          <t>658434</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>753614</t>
+          <t>749453</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1133163</t>
+          <t>1122995</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1258459</t>
+          <t>1254500</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q4502_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q4502_R-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>303463</t>
+          <t>306409</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>362754</t>
+          <t>367375</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>327643</t>
+          <t>328449</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>393343</t>
+          <t>392533</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>650658</t>
+          <t>653740</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>738820</t>
+          <t>739946</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,57%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>168754</t>
+          <t>169609</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>220268</t>
+          <t>219201</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>211077</t>
+          <t>214547</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>265752</t>
+          <t>268056</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>393808</t>
+          <t>395785</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>468536</t>
+          <t>468998</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,01%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>205596</t>
+          <t>202892</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>259648</t>
+          <t>257718</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>271464</t>
+          <t>268456</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>331599</t>
+          <t>330097</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>494430</t>
+          <t>496033</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>573455</t>
+          <t>570959</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38844</t>
+          <t>37792</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65810</t>
+          <t>66658</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57949</t>
+          <t>57237</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90971</t>
+          <t>88267</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>103149</t>
+          <t>103082</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>146542</t>
+          <t>144375</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>194020</t>
+          <t>194892</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>247434</t>
+          <t>248463</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>309428</t>
+          <t>308604</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>372022</t>
+          <t>370977</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>524362</t>
+          <t>519930</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>604739</t>
+          <t>600855</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>250810</t>
+          <t>251409</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>315162</t>
+          <t>315963</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>205489</t>
+          <t>207125</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>260817</t>
+          <t>264063</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>474589</t>
+          <t>472773</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>554602</t>
+          <t>555223</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>396977</t>
+          <t>397477</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>466690</t>
+          <t>468871</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>249494</t>
+          <t>248176</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>310057</t>
+          <t>310440</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>660587</t>
+          <t>662700</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>758826</t>
+          <t>755018</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>512957</t>
+          <t>515388</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>592531</t>
+          <t>594589</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>496734</t>
+          <t>492359</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>568935</t>
+          <t>569881</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1038788</t>
+          <t>1031867</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1138804</t>
+          <t>1139424</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81235</t>
+          <t>82564</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>118881</t>
+          <t>119959</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>118277</t>
+          <t>117154</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>161162</t>
+          <t>160742</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>211308</t>
+          <t>209684</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>268159</t>
+          <t>267263</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>290905</t>
+          <t>290086</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>362359</t>
+          <t>360874</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>368044</t>
+          <t>367890</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>435249</t>
+          <t>434869</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>682209</t>
+          <t>680468</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>774765</t>
+          <t>772800</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,59%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85755</t>
+          <t>83859</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>124968</t>
+          <t>122828</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67461</t>
+          <t>68149</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>103134</t>
+          <t>102465</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>162915</t>
+          <t>163656</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>214959</t>
+          <t>216902</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>108615</t>
+          <t>107133</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>149253</t>
+          <t>149491</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79789</t>
+          <t>78867</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>115197</t>
+          <t>113783</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>197890</t>
+          <t>195469</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>251144</t>
+          <t>251808</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>158345</t>
+          <t>159941</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>206022</t>
+          <t>203627</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>138001</t>
+          <t>138852</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>180897</t>
+          <t>180745</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>310239</t>
+          <t>311135</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>370423</t>
+          <t>369471</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,95%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33375</t>
+          <t>32584</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58781</t>
+          <t>60474</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35322</t>
+          <t>34322</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63193</t>
+          <t>61699</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74146</t>
+          <t>74446</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>109743</t>
+          <t>111341</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>76986</t>
+          <t>76785</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>113563</t>
+          <t>113124</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>72572</t>
+          <t>74890</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>108091</t>
+          <t>111013</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>161187</t>
+          <t>160479</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>209284</t>
+          <t>210603</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>671434</t>
+          <t>670653</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>767657</t>
+          <t>770502</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>634255</t>
+          <t>634543</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>731378</t>
+          <t>729963</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1330014</t>
+          <t>1335223</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1460295</t>
+          <t>1465103</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>702665</t>
+          <t>704526</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>803949</t>
+          <t>803543</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>575402</t>
+          <t>570063</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>666360</t>
+          <t>661976</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1300068</t>
+          <t>1299314</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1431197</t>
+          <t>1433515</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,57%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>913761</t>
+          <t>915692</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1020629</t>
+          <t>1019740</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>929846</t>
+          <t>935491</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1043322</t>
+          <t>1044573</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1888742</t>
+          <t>1884962</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2037541</t>
+          <t>2037002</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,64%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>168536</t>
+          <t>168925</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>222029</t>
+          <t>222485</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>229760</t>
+          <t>226090</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>288571</t>
+          <t>287801</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>411947</t>
+          <t>412587</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>493046</t>
+          <t>494237</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>592539</t>
+          <t>595817</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>683628</t>
+          <t>690060</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>775347</t>
+          <t>781416</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>876210</t>
+          <t>881237</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1402924</t>
+          <t>1404509</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1538111</t>
+          <t>1542174</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>457962</t>
+          <t>460707</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>522985</t>
+          <t>523382</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>639983</t>
+          <t>641614</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>717841</t>
+          <t>714715</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1118812</t>
+          <t>1116197</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1211418</t>
+          <t>1212282</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,47%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>136465</t>
+          <t>134445</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>185651</t>
+          <t>184311</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>159602</t>
+          <t>162039</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>212753</t>
+          <t>211525</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>316027</t>
+          <t>309193</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>382618</t>
+          <t>379601</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79051</t>
+          <t>80173</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>116496</t>
+          <t>119172</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>109272</t>
+          <t>110152</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>155120</t>
+          <t>156207</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>201929</t>
+          <t>200967</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>261436</t>
+          <t>259559</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25140</t>
+          <t>23916</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50791</t>
+          <t>49342</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32823</t>
+          <t>31966</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60238</t>
+          <t>60471</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65303</t>
+          <t>63660</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>99999</t>
+          <t>101363</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>165107</t>
+          <t>168052</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>216286</t>
+          <t>218148</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>268221</t>
+          <t>269619</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>333457</t>
+          <t>329877</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>450158</t>
+          <t>448110</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>532645</t>
+          <t>529598</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,92%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>656943</t>
+          <t>656889</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>745661</t>
+          <t>749125</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>505008</t>
+          <t>504100</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>580166</t>
+          <t>581219</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1184937</t>
+          <t>1184463</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1308245</t>
+          <t>1303213</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,09%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>420222</t>
+          <t>423904</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>498892</t>
+          <t>500244</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>328389</t>
+          <t>324845</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>397253</t>
+          <t>398210</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>766328</t>
+          <t>773573</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>870329</t>
+          <t>873059</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>341549</t>
+          <t>341216</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>417018</t>
+          <t>415593</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>309041</t>
+          <t>307866</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>376669</t>
+          <t>377530</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>675191</t>
+          <t>675127</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>776406</t>
+          <t>771034</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72325</t>
+          <t>75840</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112711</t>
+          <t>116363</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>122920</t>
+          <t>124885</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>170953</t>
+          <t>172380</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>209766</t>
+          <t>210211</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>269211</t>
+          <t>272348</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>292739</t>
+          <t>297511</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>362962</t>
+          <t>367117</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>323920</t>
+          <t>327953</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>394272</t>
+          <t>396878</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>645218</t>
+          <t>642464</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>743521</t>
+          <t>743005</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,01%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>137912</t>
+          <t>137517</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>181586</t>
+          <t>181664</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>137672</t>
+          <t>137189</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>181130</t>
+          <t>181189</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>288145</t>
+          <t>286447</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>348329</t>
+          <t>350739</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,47%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>100099</t>
+          <t>100500</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>142765</t>
+          <t>140182</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75273</t>
+          <t>73774</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>112325</t>
+          <t>110849</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>186213</t>
+          <t>183966</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>240631</t>
+          <t>240392</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,68%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>92839</t>
+          <t>89799</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>133395</t>
+          <t>130156</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>84595</t>
+          <t>83686</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>121873</t>
+          <t>121121</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>186671</t>
+          <t>187793</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>239624</t>
+          <t>243078</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,97%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17064</t>
+          <t>16827</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37760</t>
+          <t>37160</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>26318</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50967</t>
+          <t>50012</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49653</t>
+          <t>48640</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81243</t>
+          <t>81438</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50091</t>
+          <t>50964</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>83174</t>
+          <t>83750</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50545</t>
+          <t>51374</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>83061</t>
+          <t>84238</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>109184</t>
+          <t>107782</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>154233</t>
+          <t>154149</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1293263</t>
+          <t>1287590</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1407439</t>
+          <t>1408204</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1316598</t>
+          <t>1315476</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1439388</t>
+          <t>1431971</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2634298</t>
+          <t>2641706</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2807824</t>
+          <t>2807472</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>691012</t>
+          <t>683934</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>789748</t>
+          <t>788134</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>594408</t>
+          <t>597163</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>685999</t>
+          <t>686789</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1309119</t>
+          <t>1314969</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1447021</t>
+          <t>1447971</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,8%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>542828</t>
+          <t>543127</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>634222</t>
+          <t>638204</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>533374</t>
+          <t>531906</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>618643</t>
+          <t>622075</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1098594</t>
+          <t>1097982</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1229560</t>
+          <t>1227067</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>133417</t>
+          <t>130828</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>181315</t>
+          <t>179292</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>201355</t>
+          <t>197732</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>260062</t>
+          <t>257588</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>338753</t>
+          <t>344664</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>421555</t>
+          <t>425845</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>537435</t>
+          <t>535676</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>630697</t>
+          <t>627951</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>673846</t>
+          <t>675813</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>773473</t>
+          <t>774421</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1243496</t>
+          <t>1241780</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1379705</t>
+          <t>1381218</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>193033</t>
+          <t>196650</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>242934</t>
+          <t>242799</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>264031</t>
+          <t>266104</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>326261</t>
+          <t>325976</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>472813</t>
+          <t>472544</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>551385</t>
+          <t>548434</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,44%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>224525</t>
+          <t>224595</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>276682</t>
+          <t>275036</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>257224</t>
+          <t>253257</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>317180</t>
+          <t>316371</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>497219</t>
+          <t>491345</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>577898</t>
+          <t>571897</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,78%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>101272</t>
+          <t>101731</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>141756</t>
+          <t>140590</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>114315</t>
+          <t>115079</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>159324</t>
+          <t>159722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>230022</t>
+          <t>230067</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>291906</t>
+          <t>290849</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16964</t>
+          <t>17667</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37089</t>
+          <t>36903</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28817</t>
+          <t>28032</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54831</t>
+          <t>53525</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49916</t>
+          <t>49861</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82703</t>
+          <t>84401</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>119654</t>
+          <t>117273</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>160163</t>
+          <t>160910</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>213539</t>
+          <t>208708</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>269800</t>
+          <t>268631</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>343105</t>
+          <t>341112</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>413924</t>
+          <t>412598</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>437353</t>
+          <t>439541</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>522459</t>
+          <t>517261</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>385074</t>
+          <t>381713</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>456778</t>
+          <t>459642</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>841581</t>
+          <t>839560</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>953280</t>
+          <t>948915</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>596840</t>
+          <t>597713</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>685562</t>
+          <t>688176</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>585728</t>
+          <t>580360</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>671218</t>
+          <t>667742</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1207211</t>
+          <t>1209801</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1329170</t>
+          <t>1331302</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,9%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>492721</t>
+          <t>490009</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>567957</t>
+          <t>570750</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>401148</t>
+          <t>401684</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>477823</t>
+          <t>475333</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>913679</t>
+          <t>913073</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1021798</t>
+          <t>1021613</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>110085</t>
+          <t>110010</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>155265</t>
+          <t>157357</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>123563</t>
+          <t>121678</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>170677</t>
+          <t>168201</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>241267</t>
+          <t>241407</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>308404</t>
+          <t>311128</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>256758</t>
+          <t>258431</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>321749</t>
+          <t>321615</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>320077</t>
+          <t>314600</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>387613</t>
+          <t>385194</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>594547</t>
+          <t>595561</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>686481</t>
+          <t>694401</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>108494</t>
+          <t>107189</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>148228</t>
+          <t>147986</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>103486</t>
+          <t>103365</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>144468</t>
+          <t>145586</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>223868</t>
+          <t>222198</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>281679</t>
+          <t>282217</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>178846</t>
+          <t>180749</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>226033</t>
+          <t>226650</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123388</t>
+          <t>128220</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>169470</t>
+          <t>169078</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>317724</t>
+          <t>317386</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>379958</t>
+          <t>379853</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,78%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>98619</t>
+          <t>96954</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>137703</t>
+          <t>137528</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>108595</t>
+          <t>106684</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>148452</t>
+          <t>146526</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>219284</t>
+          <t>219280</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274348</t>
+          <t>273463</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21863</t>
+          <t>21902</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44248</t>
+          <t>44058</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30357</t>
+          <t>30392</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56011</t>
+          <t>56843</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56465</t>
+          <t>59864</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>91830</t>
+          <t>93414</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>47285</t>
+          <t>47080</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>79591</t>
+          <t>79003</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>92045</t>
+          <t>92121</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>131703</t>
+          <t>131915</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>148649</t>
+          <t>147035</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>199686</t>
+          <t>199888</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>773716</t>
+          <t>779031</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>872934</t>
+          <t>880186</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>783132</t>
+          <t>786001</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>881751</t>
+          <t>885141</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1586580</t>
+          <t>1587401</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1736116</t>
+          <t>1739684</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1035492</t>
+          <t>1038974</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1147853</t>
+          <t>1144131</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1003908</t>
+          <t>999262</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1115380</t>
+          <t>1106759</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2072351</t>
+          <t>2064917</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2227707</t>
+          <t>2223550</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,31%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>722357</t>
+          <t>718559</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>820400</t>
+          <t>818671</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>653981</t>
+          <t>653978</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>746642</t>
+          <t>749928</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1408513</t>
+          <t>1400755</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1543978</t>
+          <t>1540544</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>163177</t>
+          <t>165006</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>217221</t>
+          <t>217595</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>198582</t>
+          <t>198221</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>256435</t>
+          <t>258928</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>375185</t>
+          <t>375177</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>459141</t>
+          <t>452409</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>450306</t>
+          <t>450557</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>533695</t>
+          <t>528981</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>658434</t>
+          <t>648769</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>749453</t>
+          <t>744604</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1122995</t>
+          <t>1125177</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1254500</t>
+          <t>1257417</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
